--- a/docs/example.xlsx
+++ b/docs/example.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\infinitebrain-backoffice\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6426C081-7B80-4C87-9978-9DE813447571}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2663C732-37EB-42CB-84FF-B8B0B19B8CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7DE74825-8723-484D-9D59-A538298747FB}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7DE74825-8723-484D-9D59-A538298747FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>เลขที่   ...............................................................................</t>
   </si>
@@ -84,9 +84,6 @@
   </si>
   <si>
     <t>ลำดับที่ / NO.</t>
-  </si>
-  <si>
-    <t>การเช่าอสังหาริมทรัพย์ อัลไล</t>
   </si>
   <si>
     <t>23/01/2026</t>
@@ -112,15 +109,9 @@
     </r>
   </si>
   <si>
-    <t>บริษัท ทรัสต์เพื่อการลงทุนในสิทธิ</t>
-  </si>
-  <si>
     <t>จ่ายให้ / Pay to</t>
   </si>
   <si>
-    <t>EL20260112</t>
-  </si>
-  <si>
     <t xml:space="preserve">เลขที่ / Voucher NO.   </t>
   </si>
   <si>
@@ -154,7 +145,13 @@
     <t>ที่อยู่</t>
   </si>
   <si>
-    <t>testtttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttttt</t>
+    <t>address</t>
+  </si>
+  <si>
+    <t>บริษัท ทรัสต์เพื่อการลงทุนในสิทธิ การเช่าอสังหาริมทรัพย์ อัลไล</t>
+  </si>
+  <si>
+    <t>EL20260101</t>
   </si>
 </sst>
 </file>
@@ -382,7 +379,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -420,7 +417,6 @@
     </xf>
     <xf numFmtId="40" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="14" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -446,6 +442,66 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -458,15 +514,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -485,59 +532,8 @@
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -980,265 +976,263 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="D1" s="30"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="30"/>
-      <c r="G1" s="30"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
+      <c r="A1" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="29"/>
+      <c r="E1" s="29"/>
+      <c r="F1" s="29"/>
+      <c r="G1" s="29"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
     </row>
     <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="27"/>
-      <c r="B2" s="27"/>
-      <c r="C2" s="31" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="30"/>
-      <c r="G2" s="30"/>
-      <c r="H2" s="26"/>
-      <c r="I2" s="26"/>
-      <c r="J2" s="26"/>
+      <c r="A2" s="26"/>
+      <c r="B2" s="26"/>
+      <c r="C2" s="30" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
     </row>
     <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="27"/>
-      <c r="B3" s="27"/>
-      <c r="C3" s="31" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" s="30"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="30"/>
-      <c r="G3" s="30"/>
-      <c r="H3" s="26"/>
-      <c r="I3" s="26"/>
-      <c r="J3" s="26"/>
+      <c r="A3" s="26"/>
+      <c r="B3" s="26"/>
+      <c r="C3" s="30" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="29"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="29"/>
+      <c r="G3" s="29"/>
+      <c r="H3" s="25"/>
+      <c r="I3" s="25"/>
+      <c r="J3" s="25"/>
     </row>
     <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="27"/>
-      <c r="B4" s="27"/>
-      <c r="C4" s="29" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="27"/>
-      <c r="I4" s="26"/>
-      <c r="J4" s="26"/>
+      <c r="A4" s="26"/>
+      <c r="B4" s="26"/>
+      <c r="C4" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="27"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="26"/>
+      <c r="I4" s="25"/>
+      <c r="J4" s="25"/>
     </row>
     <row r="5" spans="1:10" ht="21.75" x14ac:dyDescent="0.5">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" s="24"/>
-      <c r="G5" s="24"/>
-      <c r="H5" s="23"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="23"/>
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
     </row>
     <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="49" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
+      <c r="A6" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="50"/>
-      <c r="J7" s="50"/>
+      <c r="A7" s="41" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="41"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="41"/>
+      <c r="I7" s="41"/>
+      <c r="J7" s="41"/>
     </row>
     <row r="8" spans="1:10" ht="21.75" x14ac:dyDescent="0.5">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="21"/>
-      <c r="J8" s="19"/>
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="20"/>
+      <c r="J8" s="18"/>
     </row>
     <row r="9" spans="1:10" ht="21.75" x14ac:dyDescent="0.5">
-      <c r="A9" s="21"/>
+      <c r="A9" s="20"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="21"/>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-    </row>
-    <row r="10" spans="1:10" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A10" s="52" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="52"/>
-      <c r="C10" s="53" t="s">
+      <c r="C9" s="20"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="20"/>
+      <c r="G9" s="20"/>
+    </row>
+    <row r="10" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="36" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="36"/>
+      <c r="C10" s="62" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="62"/>
+      <c r="E10" s="62"/>
+      <c r="F10" s="62"/>
+      <c r="G10" s="62"/>
+      <c r="H10" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="51" t="s">
-        <v>22</v>
-      </c>
-      <c r="I10" s="51"/>
-      <c r="J10" s="20" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="I10" s="42"/>
+      <c r="J10" s="19" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="17" t="s">
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
+      <c r="G11" s="62"/>
+      <c r="H11" s="35" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="35"/>
+      <c r="J11" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="58" t="s">
-        <v>18</v>
-      </c>
-      <c r="I11" s="58"/>
-      <c r="J11" s="18" t="s">
-        <v>17</v>
-      </c>
     </row>
     <row r="12" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A12" s="52" t="s">
+      <c r="A12" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="B12" s="36"/>
+      <c r="C12" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="D12" s="37"/>
+      <c r="E12" s="37"/>
+      <c r="F12" s="37"/>
+      <c r="G12" s="37"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="17"/>
+    </row>
+    <row r="13" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
+      <c r="A13" s="31"/>
+      <c r="B13" s="31"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="33"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="17"/>
+    </row>
+    <row r="14" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="38" t="s">
+        <v>29</v>
+      </c>
+      <c r="B14" s="38"/>
+      <c r="C14" s="39" t="s">
         <v>30</v>
       </c>
-      <c r="B12" s="52"/>
-      <c r="C12" s="60" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="60"/>
-      <c r="E12" s="60"/>
-      <c r="F12" s="60"/>
-      <c r="G12" s="60"/>
-      <c r="H12" s="59"/>
-      <c r="I12" s="59"/>
-      <c r="J12" s="18"/>
-    </row>
-    <row r="13" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A13" s="32"/>
-      <c r="B13" s="32"/>
-      <c r="C13" s="61"/>
-      <c r="D13" s="61"/>
-      <c r="E13" s="61"/>
-      <c r="F13" s="61"/>
-      <c r="G13" s="61"/>
-      <c r="H13" s="59"/>
-      <c r="I13" s="59"/>
-      <c r="J13" s="18"/>
-    </row>
-    <row r="14" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="62" t="s">
-        <v>32</v>
-      </c>
-      <c r="B14" s="62"/>
-      <c r="C14" s="63" t="s">
-        <v>33</v>
-      </c>
-      <c r="D14" s="63"/>
-      <c r="E14" s="63"/>
-      <c r="F14" s="63"/>
-      <c r="G14" s="63"/>
-      <c r="H14" s="59"/>
-      <c r="I14" s="59"/>
-      <c r="J14" s="18"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="32"/>
+      <c r="J14" s="17"/>
     </row>
     <row r="15" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="62"/>
-      <c r="B15" s="62"/>
-      <c r="C15" s="63"/>
-      <c r="D15" s="63"/>
-      <c r="E15" s="63"/>
-      <c r="F15" s="63"/>
-      <c r="G15" s="63"/>
-      <c r="H15" s="59"/>
-      <c r="I15" s="59"/>
-      <c r="J15" s="18"/>
+      <c r="A15" s="38"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="39"/>
+      <c r="G15" s="39"/>
+      <c r="H15" s="32"/>
+      <c r="I15" s="32"/>
+      <c r="J15" s="17"/>
     </row>
     <row r="16" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A16" s="32"/>
-      <c r="B16" s="32"/>
-      <c r="C16" s="61"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="61"/>
-      <c r="G16" s="61"/>
-      <c r="H16" s="59"/>
-      <c r="I16" s="59"/>
-      <c r="J16" s="18"/>
+      <c r="A16" s="31"/>
+      <c r="B16" s="31"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="33"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="33"/>
+      <c r="G16" s="33"/>
+      <c r="H16" s="32"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="17"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="54" t="s">
+      <c r="A17" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38" t="s">
+      <c r="B17" s="44"/>
+      <c r="C17" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38" t="s">
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="J17" s="56"/>
+      <c r="J17" s="47"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="55"/>
-      <c r="B18" s="39"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="57"/>
+      <c r="A18" s="45"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="46"/>
+      <c r="J18" s="48"/>
     </row>
     <row r="19" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="37">
+      <c r="A19" s="34">
         <v>1</v>
       </c>
-      <c r="B19" s="37"/>
+      <c r="B19" s="34"/>
       <c r="C19" s="8" t="s">
         <v>12</v>
       </c>
@@ -1248,15 +1242,15 @@
       <c r="G19" s="11"/>
       <c r="H19" s="16"/>
       <c r="I19" s="15">
-        <v>59403.95</v>
+        <v>100000</v>
       </c>
       <c r="J19" s="6"/>
     </row>
     <row r="20" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A20" s="37">
+      <c r="A20" s="34">
         <v>2</v>
       </c>
-      <c r="B20" s="37"/>
+      <c r="B20" s="34"/>
       <c r="C20" s="8" t="s">
         <v>11</v>
       </c>
@@ -1266,15 +1260,15 @@
       <c r="G20" s="7"/>
       <c r="H20" s="12"/>
       <c r="I20" s="14">
-        <v>42375.43</v>
+        <v>100000</v>
       </c>
       <c r="J20" s="6"/>
     </row>
     <row r="21" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A21" s="37">
+      <c r="A21" s="34">
         <v>3</v>
       </c>
-      <c r="B21" s="37"/>
+      <c r="B21" s="34"/>
       <c r="C21" s="8" t="s">
         <v>10</v>
       </c>
@@ -1284,15 +1278,15 @@
       <c r="G21" s="7"/>
       <c r="H21" s="9"/>
       <c r="I21" s="14">
-        <v>7425.49</v>
+        <v>100000</v>
       </c>
       <c r="J21" s="6"/>
     </row>
     <row r="22" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A22" s="37">
+      <c r="A22" s="34">
         <v>4</v>
       </c>
-      <c r="B22" s="37"/>
+      <c r="B22" s="34"/>
       <c r="C22" s="8" t="s">
         <v>9</v>
       </c>
@@ -1302,7 +1296,7 @@
       <c r="G22" s="7"/>
       <c r="H22" s="9"/>
       <c r="I22" s="14">
-        <v>7550.19</v>
+        <v>100000</v>
       </c>
       <c r="J22" s="6"/>
     </row>
@@ -1343,8 +1337,8 @@
       <c r="J25" s="6"/>
     </row>
     <row r="26" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A26" s="37"/>
-      <c r="B26" s="37"/>
+      <c r="A26" s="34"/>
+      <c r="B26" s="34"/>
       <c r="C26" s="8"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
@@ -1355,8 +1349,8 @@
       <c r="J26" s="6"/>
     </row>
     <row r="27" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A27" s="37"/>
-      <c r="B27" s="37"/>
+      <c r="A27" s="34"/>
+      <c r="B27" s="34"/>
       <c r="C27" s="8"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
@@ -1367,8 +1361,8 @@
       <c r="J27" s="6"/>
     </row>
     <row r="28" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A28" s="37"/>
-      <c r="B28" s="37"/>
+      <c r="A28" s="34"/>
+      <c r="B28" s="34"/>
       <c r="C28" s="8"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
@@ -1379,8 +1373,8 @@
       <c r="J28" s="6"/>
     </row>
     <row r="29" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A29" s="37"/>
-      <c r="B29" s="37"/>
+      <c r="A29" s="34"/>
+      <c r="B29" s="34"/>
       <c r="C29" s="8"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
@@ -1391,59 +1385,59 @@
       <c r="J29" s="6"/>
     </row>
     <row r="30" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A30" s="37"/>
-      <c r="B30" s="37"/>
-      <c r="C30" s="44"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="45"/>
+      <c r="A30" s="34"/>
+      <c r="B30" s="34"/>
+      <c r="C30" s="60"/>
+      <c r="D30" s="60"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="60"/>
+      <c r="G30" s="60"/>
+      <c r="H30" s="60"/>
+      <c r="I30" s="61"/>
+      <c r="J30" s="61"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="46"/>
-      <c r="B31" s="46"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="47"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="48"/>
-      <c r="J31" s="48"/>
+      <c r="A31" s="49"/>
+      <c r="B31" s="49"/>
+      <c r="C31" s="50"/>
+      <c r="D31" s="50"/>
+      <c r="E31" s="50"/>
+      <c r="F31" s="50"/>
+      <c r="G31" s="50"/>
+      <c r="H31" s="50"/>
+      <c r="I31" s="51"/>
+      <c r="J31" s="51"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
-      <c r="C32" s="38" t="s">
+      <c r="C32" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="D32" s="38"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="38"/>
-      <c r="H32" s="38"/>
-      <c r="I32" s="40">
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="56">
         <f>SUM(I19:I31)</f>
-        <v>116755.06000000001</v>
-      </c>
-      <c r="J32" s="42" t="s">
+        <v>400000</v>
+      </c>
+      <c r="J32" s="58" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="39"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="41"/>
-      <c r="J33" s="43"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="46"/>
+      <c r="I33" s="57"/>
+      <c r="J33" s="59"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
@@ -1458,64 +1452,64 @@
       <c r="J34" s="2"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="33" t="s">
+      <c r="A35" s="52" t="s">
         <v>6</v>
       </c>
-      <c r="B35" s="33"/>
-      <c r="C35" s="33"/>
-      <c r="D35" s="34" t="s">
+      <c r="B35" s="52"/>
+      <c r="C35" s="52"/>
+      <c r="D35" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="35" t="s">
+      <c r="E35" s="53"/>
+      <c r="F35" s="53"/>
+      <c r="G35" s="53"/>
+      <c r="H35" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="I35" s="35"/>
-      <c r="J35" s="35"/>
+      <c r="I35" s="54"/>
+      <c r="J35" s="54"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="33"/>
-      <c r="B36" s="33"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="35"/>
-      <c r="J36" s="35"/>
+      <c r="A36" s="52"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="53"/>
+      <c r="E36" s="53"/>
+      <c r="F36" s="53"/>
+      <c r="G36" s="53"/>
+      <c r="H36" s="54"/>
+      <c r="I36" s="54"/>
+      <c r="J36" s="54"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="33" t="s">
+      <c r="A37" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="B37" s="33"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="34" t="s">
+      <c r="B37" s="52"/>
+      <c r="C37" s="52"/>
+      <c r="D37" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="34"/>
-      <c r="H37" s="35" t="s">
+      <c r="E37" s="53"/>
+      <c r="F37" s="53"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="54" t="s">
         <v>1</v>
       </c>
-      <c r="I37" s="35"/>
-      <c r="J37" s="35"/>
+      <c r="I37" s="54"/>
+      <c r="J37" s="54"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="33"/>
-      <c r="B38" s="33"/>
-      <c r="C38" s="33"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="35"/>
-      <c r="I38" s="35"/>
-      <c r="J38" s="35"/>
+      <c r="A38" s="52"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="52"/>
+      <c r="D38" s="53"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="53"/>
+      <c r="H38" s="54"/>
+      <c r="I38" s="54"/>
+      <c r="J38" s="54"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
@@ -1525,35 +1519,14 @@
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
-      <c r="H39" s="36" t="s">
+      <c r="H39" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="I39" s="36"/>
-      <c r="J39" s="36"/>
+      <c r="I39" s="55"/>
+      <c r="J39" s="55"/>
     </row>
   </sheetData>
   <mergeCells count="37">
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:G15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="A17:B18"/>
-    <mergeCell ref="C17:H18"/>
-    <mergeCell ref="I17:J18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
     <mergeCell ref="A37:C38"/>
     <mergeCell ref="D37:G38"/>
     <mergeCell ref="H37:J38"/>
@@ -1570,6 +1543,27 @@
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:H30"/>
     <mergeCell ref="I30:J30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="C10:G11"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:G15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C17:H18"/>
+    <mergeCell ref="I17:J18"/>
+    <mergeCell ref="A19:B19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/docs/example.xlsx
+++ b/docs/example.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\infinitebrain-backoffice\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2663C732-37EB-42CB-84FF-B8B0B19B8CD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9322E5C-F34E-4020-88AC-AE480F5FFF0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7DE74825-8723-484D-9D59-A538298747FB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
   <si>
     <t>เลขที่   ...............................................................................</t>
   </si>
@@ -153,12 +153,15 @@
   <si>
     <t>EL20260101</t>
   </si>
+  <si>
+    <t xml:space="preserve">ภาษีเงินได้หัก ณ ที่จ่าย. 3 % </t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -293,6 +296,12 @@
     <font>
       <sz val="8"/>
       <name val="Bahnschrift Light SemiCondensed"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Leelawadee UI"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -379,7 +388,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -411,7 +420,6 @@
     <xf numFmtId="40" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="40" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="40" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -448,15 +456,72 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -466,75 +531,29 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="40" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -976,263 +995,263 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="25" t="s">
         <v>26</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="30" t="s">
+      <c r="B1" s="25"/>
+      <c r="C1" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="D1" s="29"/>
-      <c r="E1" s="29"/>
-      <c r="F1" s="29"/>
-      <c r="G1" s="29"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
     </row>
     <row r="2" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="26"/>
-      <c r="B2" s="26"/>
-      <c r="C2" s="30" t="s">
+      <c r="A2" s="25"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
     </row>
     <row r="3" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="26"/>
-      <c r="B3" s="26"/>
-      <c r="C3" s="30" t="s">
+      <c r="A3" s="25"/>
+      <c r="B3" s="25"/>
+      <c r="C3" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
-      <c r="H3" s="25"/>
-      <c r="I3" s="25"/>
-      <c r="J3" s="25"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
     </row>
     <row r="4" spans="1:10" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="A4" s="26"/>
-      <c r="B4" s="26"/>
-      <c r="C4" s="28" t="s">
+      <c r="A4" s="25"/>
+      <c r="B4" s="25"/>
+      <c r="C4" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="27"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="27"/>
-      <c r="G4" s="27"/>
-      <c r="H4" s="26"/>
-      <c r="I4" s="25"/>
-      <c r="J4" s="25"/>
+      <c r="D4" s="26"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="26"/>
+      <c r="H4" s="25"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
     </row>
     <row r="5" spans="1:10" ht="21.75" x14ac:dyDescent="0.5">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="23"/>
-      <c r="E5" s="23"/>
-      <c r="F5" s="23"/>
-      <c r="G5" s="23"/>
-      <c r="H5" s="22"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
     </row>
     <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="40" t="s">
+      <c r="A6" s="49" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="40"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49"/>
+      <c r="F6" s="49"/>
+      <c r="G6" s="49"/>
+      <c r="H6" s="49"/>
+      <c r="I6" s="49"/>
+      <c r="J6" s="49"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="41" t="s">
+      <c r="A7" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="41"/>
-      <c r="H7" s="41"/>
-      <c r="I7" s="41"/>
-      <c r="J7" s="41"/>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="50"/>
+      <c r="F7" s="50"/>
+      <c r="G7" s="50"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="50"/>
+      <c r="J7" s="50"/>
     </row>
     <row r="8" spans="1:10" ht="21.75" x14ac:dyDescent="0.5">
       <c r="A8" s="2"/>
       <c r="B8" s="2"/>
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="18"/>
+      <c r="C8" s="20"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="20"/>
+      <c r="F8" s="20"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="17"/>
     </row>
     <row r="9" spans="1:10" ht="21.75" x14ac:dyDescent="0.5">
-      <c r="A9" s="20"/>
+      <c r="A9" s="19"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="20"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="20"/>
-      <c r="F9" s="20"/>
-      <c r="G9" s="20"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
     </row>
     <row r="10" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="51" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="36"/>
-      <c r="C10" s="62" t="s">
+      <c r="B10" s="51"/>
+      <c r="C10" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="D10" s="62"/>
-      <c r="E10" s="62"/>
-      <c r="F10" s="62"/>
-      <c r="G10" s="62"/>
-      <c r="H10" s="42" t="s">
+      <c r="D10" s="53"/>
+      <c r="E10" s="53"/>
+      <c r="F10" s="53"/>
+      <c r="G10" s="53"/>
+      <c r="H10" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="I10" s="42"/>
-      <c r="J10" s="19" t="s">
+      <c r="I10" s="52"/>
+      <c r="J10" s="18" t="s">
         <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
       <c r="B11" s="2"/>
-      <c r="C11" s="62"/>
-      <c r="D11" s="62"/>
-      <c r="E11" s="62"/>
-      <c r="F11" s="62"/>
-      <c r="G11" s="62"/>
-      <c r="H11" s="35" t="s">
+      <c r="C11" s="53"/>
+      <c r="D11" s="53"/>
+      <c r="E11" s="53"/>
+      <c r="F11" s="53"/>
+      <c r="G11" s="53"/>
+      <c r="H11" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="35"/>
-      <c r="J11" s="17" t="s">
+      <c r="I11" s="54"/>
+      <c r="J11" s="16" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A12" s="36" t="s">
+      <c r="A12" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="36"/>
-      <c r="C12" s="37" t="s">
+      <c r="B12" s="51"/>
+      <c r="C12" s="55" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="37"/>
-      <c r="E12" s="37"/>
-      <c r="F12" s="37"/>
-      <c r="G12" s="37"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="32"/>
-      <c r="J12" s="17"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="16"/>
     </row>
     <row r="13" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A13" s="31"/>
-      <c r="B13" s="31"/>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="33"/>
-      <c r="G13" s="33"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="32"/>
-      <c r="J13" s="17"/>
+      <c r="A13" s="30"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="16"/>
     </row>
     <row r="14" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="56" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="38"/>
-      <c r="C14" s="39" t="s">
+      <c r="B14" s="56"/>
+      <c r="C14" s="57" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
-      <c r="F14" s="39"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="32"/>
-      <c r="J14" s="17"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="16"/>
     </row>
     <row r="15" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="38"/>
-      <c r="B15" s="38"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
-      <c r="F15" s="39"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="32"/>
-      <c r="I15" s="32"/>
-      <c r="J15" s="17"/>
+      <c r="A15" s="56"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="16"/>
     </row>
     <row r="16" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A16" s="31"/>
-      <c r="B16" s="31"/>
-      <c r="C16" s="33"/>
-      <c r="D16" s="33"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="33"/>
-      <c r="G16" s="33"/>
-      <c r="H16" s="32"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="17"/>
+      <c r="A16" s="30"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="32"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="16"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="43" t="s">
+      <c r="A17" s="58" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="44"/>
-      <c r="C17" s="44" t="s">
+      <c r="B17" s="38"/>
+      <c r="C17" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="44"/>
-      <c r="E17" s="44"/>
-      <c r="F17" s="44"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="44"/>
-      <c r="I17" s="44" t="s">
+      <c r="D17" s="38"/>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38"/>
+      <c r="G17" s="38"/>
+      <c r="H17" s="38"/>
+      <c r="I17" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="J17" s="47"/>
+      <c r="J17" s="60"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="45"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="46"/>
-      <c r="E18" s="46"/>
-      <c r="F18" s="46"/>
-      <c r="G18" s="46"/>
-      <c r="H18" s="46"/>
-      <c r="I18" s="46"/>
-      <c r="J18" s="48"/>
+      <c r="A18" s="59"/>
+      <c r="B18" s="39"/>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="39"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="39"/>
+      <c r="J18" s="61"/>
     </row>
     <row r="19" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A19" s="34">
+      <c r="A19" s="37">
         <v>1</v>
       </c>
-      <c r="B19" s="34"/>
+      <c r="B19" s="37"/>
       <c r="C19" s="8" t="s">
         <v>12</v>
       </c>
@@ -1240,17 +1259,17 @@
       <c r="E19" s="11"/>
       <c r="F19" s="11"/>
       <c r="G19" s="11"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="15">
+      <c r="H19" s="15"/>
+      <c r="I19" s="14">
         <v>100000</v>
       </c>
       <c r="J19" s="6"/>
     </row>
     <row r="20" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A20" s="34">
+      <c r="A20" s="37">
         <v>2</v>
       </c>
-      <c r="B20" s="34"/>
+      <c r="B20" s="37"/>
       <c r="C20" s="8" t="s">
         <v>11</v>
       </c>
@@ -1259,16 +1278,16 @@
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
       <c r="H20" s="12"/>
-      <c r="I20" s="14">
+      <c r="I20" s="13">
         <v>100000</v>
       </c>
       <c r="J20" s="6"/>
     </row>
     <row r="21" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A21" s="34">
+      <c r="A21" s="37">
         <v>3</v>
       </c>
-      <c r="B21" s="34"/>
+      <c r="B21" s="37"/>
       <c r="C21" s="8" t="s">
         <v>10</v>
       </c>
@@ -1277,16 +1296,16 @@
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="14">
+      <c r="I21" s="13">
         <v>100000</v>
       </c>
       <c r="J21" s="6"/>
     </row>
     <row r="22" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A22" s="34">
+      <c r="A22" s="37">
         <v>4</v>
       </c>
-      <c r="B22" s="34"/>
+      <c r="B22" s="37"/>
       <c r="C22" s="8" t="s">
         <v>9</v>
       </c>
@@ -1295,21 +1314,27 @@
       <c r="F22" s="11"/>
       <c r="G22" s="7"/>
       <c r="H22" s="9"/>
-      <c r="I22" s="14">
+      <c r="I22" s="13">
         <v>100000</v>
       </c>
       <c r="J22" s="6"/>
     </row>
     <row r="23" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A23" s="5"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="8"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="11"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="6"/>
+      <c r="A23" s="62">
+        <v>5</v>
+      </c>
+      <c r="B23" s="62"/>
+      <c r="C23" s="63"/>
+      <c r="D23" s="63"/>
+      <c r="E23" s="63" t="s">
+        <v>33</v>
+      </c>
+      <c r="F23" s="63"/>
+      <c r="G23" s="64"/>
+      <c r="H23" s="65"/>
+      <c r="I23" s="66">
+        <v>-12000</v>
+      </c>
       <c r="J23" s="6"/>
     </row>
     <row r="24" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
@@ -1337,8 +1362,8 @@
       <c r="J25" s="6"/>
     </row>
     <row r="26" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A26" s="34"/>
-      <c r="B26" s="34"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="37"/>
       <c r="C26" s="8"/>
       <c r="D26" s="7"/>
       <c r="E26" s="7"/>
@@ -1349,8 +1374,8 @@
       <c r="J26" s="6"/>
     </row>
     <row r="27" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A27" s="34"/>
-      <c r="B27" s="34"/>
+      <c r="A27" s="37"/>
+      <c r="B27" s="37"/>
       <c r="C27" s="8"/>
       <c r="D27" s="7"/>
       <c r="E27" s="7"/>
@@ -1361,8 +1386,8 @@
       <c r="J27" s="6"/>
     </row>
     <row r="28" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A28" s="34"/>
-      <c r="B28" s="34"/>
+      <c r="A28" s="37"/>
+      <c r="B28" s="37"/>
       <c r="C28" s="8"/>
       <c r="D28" s="7"/>
       <c r="E28" s="7"/>
@@ -1373,8 +1398,8 @@
       <c r="J28" s="6"/>
     </row>
     <row r="29" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A29" s="34"/>
-      <c r="B29" s="34"/>
+      <c r="A29" s="37"/>
+      <c r="B29" s="37"/>
       <c r="C29" s="8"/>
       <c r="D29" s="7"/>
       <c r="E29" s="7"/>
@@ -1385,59 +1410,59 @@
       <c r="J29" s="6"/>
     </row>
     <row r="30" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A30" s="34"/>
-      <c r="B30" s="34"/>
-      <c r="C30" s="60"/>
-      <c r="D30" s="60"/>
-      <c r="E30" s="60"/>
-      <c r="F30" s="60"/>
-      <c r="G30" s="60"/>
-      <c r="H30" s="60"/>
-      <c r="I30" s="61"/>
-      <c r="J30" s="61"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="37"/>
+      <c r="C30" s="44"/>
+      <c r="D30" s="44"/>
+      <c r="E30" s="44"/>
+      <c r="F30" s="44"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="44"/>
+      <c r="I30" s="45"/>
+      <c r="J30" s="45"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="49"/>
-      <c r="B31" s="49"/>
-      <c r="C31" s="50"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="50"/>
-      <c r="I31" s="51"/>
-      <c r="J31" s="51"/>
+      <c r="A31" s="46"/>
+      <c r="B31" s="46"/>
+      <c r="C31" s="47"/>
+      <c r="D31" s="47"/>
+      <c r="E31" s="47"/>
+      <c r="F31" s="47"/>
+      <c r="G31" s="47"/>
+      <c r="H31" s="47"/>
+      <c r="I31" s="48"/>
+      <c r="J31" s="48"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
-      <c r="C32" s="44" t="s">
+      <c r="C32" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="D32" s="44"/>
-      <c r="E32" s="44"/>
-      <c r="F32" s="44"/>
-      <c r="G32" s="44"/>
-      <c r="H32" s="44"/>
-      <c r="I32" s="56">
+      <c r="D32" s="38"/>
+      <c r="E32" s="38"/>
+      <c r="F32" s="38"/>
+      <c r="G32" s="38"/>
+      <c r="H32" s="38"/>
+      <c r="I32" s="40">
         <f>SUM(I19:I31)</f>
-        <v>400000</v>
-      </c>
-      <c r="J32" s="58" t="s">
+        <v>388000</v>
+      </c>
+      <c r="J32" s="42" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
-      <c r="C33" s="46"/>
-      <c r="D33" s="46"/>
-      <c r="E33" s="46"/>
-      <c r="F33" s="46"/>
-      <c r="G33" s="46"/>
-      <c r="H33" s="46"/>
-      <c r="I33" s="57"/>
-      <c r="J33" s="59"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="39"/>
+      <c r="F33" s="39"/>
+      <c r="G33" s="39"/>
+      <c r="H33" s="39"/>
+      <c r="I33" s="41"/>
+      <c r="J33" s="43"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
@@ -1452,64 +1477,64 @@
       <c r="J34" s="2"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="52" t="s">
+      <c r="A35" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="B35" s="52"/>
-      <c r="C35" s="52"/>
-      <c r="D35" s="53" t="s">
+      <c r="B35" s="33"/>
+      <c r="C35" s="33"/>
+      <c r="D35" s="34" t="s">
         <v>5</v>
       </c>
-      <c r="E35" s="53"/>
-      <c r="F35" s="53"/>
-      <c r="G35" s="53"/>
-      <c r="H35" s="54" t="s">
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="35" t="s">
         <v>4</v>
       </c>
-      <c r="I35" s="54"/>
-      <c r="J35" s="54"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="35"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="52"/>
-      <c r="B36" s="52"/>
-      <c r="C36" s="52"/>
-      <c r="D36" s="53"/>
-      <c r="E36" s="53"/>
-      <c r="F36" s="53"/>
-      <c r="G36" s="53"/>
-      <c r="H36" s="54"/>
-      <c r="I36" s="54"/>
-      <c r="J36" s="54"/>
+      <c r="A36" s="33"/>
+      <c r="B36" s="33"/>
+      <c r="C36" s="33"/>
+      <c r="D36" s="34"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="35"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="52" t="s">
+      <c r="A37" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="B37" s="52"/>
-      <c r="C37" s="52"/>
-      <c r="D37" s="53" t="s">
+      <c r="B37" s="33"/>
+      <c r="C37" s="33"/>
+      <c r="D37" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="E37" s="53"/>
-      <c r="F37" s="53"/>
-      <c r="G37" s="53"/>
-      <c r="H37" s="54" t="s">
+      <c r="E37" s="34"/>
+      <c r="F37" s="34"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="I37" s="54"/>
-      <c r="J37" s="54"/>
+      <c r="I37" s="35"/>
+      <c r="J37" s="35"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="52"/>
-      <c r="B38" s="52"/>
-      <c r="C38" s="52"/>
-      <c r="D38" s="53"/>
-      <c r="E38" s="53"/>
-      <c r="F38" s="53"/>
-      <c r="G38" s="53"/>
-      <c r="H38" s="54"/>
-      <c r="I38" s="54"/>
-      <c r="J38" s="54"/>
+      <c r="A38" s="33"/>
+      <c r="B38" s="33"/>
+      <c r="C38" s="33"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="34"/>
+      <c r="F38" s="34"/>
+      <c r="G38" s="34"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="35"/>
+      <c r="J38" s="35"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
@@ -1519,14 +1544,36 @@
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
-      <c r="H39" s="55" t="s">
+      <c r="H39" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="I39" s="55"/>
-      <c r="J39" s="55"/>
+      <c r="I39" s="36"/>
+      <c r="J39" s="36"/>
     </row>
   </sheetData>
-  <mergeCells count="37">
+  <mergeCells count="38">
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:G15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C17:H18"/>
+    <mergeCell ref="I17:J18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="C10:G11"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
     <mergeCell ref="A37:C38"/>
     <mergeCell ref="D37:G38"/>
     <mergeCell ref="H37:J38"/>
@@ -1543,27 +1590,6 @@
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:H30"/>
     <mergeCell ref="I30:J30"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="C10:G11"/>
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:G15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A17:B18"/>
-    <mergeCell ref="C17:H18"/>
-    <mergeCell ref="I17:J18"/>
-    <mergeCell ref="A19:B19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>

--- a/docs/example.xlsx
+++ b/docs/example.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\infinitebrain-backoffice\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9322E5C-F34E-4020-88AC-AE480F5FFF0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6666C42-59E6-47F7-B6B8-5DB011DC3CC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{7DE74825-8723-484D-9D59-A538298747FB}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>เลขที่   ...............................................................................</t>
   </si>
@@ -155,6 +155,9 @@
   </si>
   <si>
     <t xml:space="preserve">ภาษีเงินได้หัก ณ ที่จ่าย. 3 % </t>
+  </si>
+  <si>
+    <t>เบิกจ่ายประจำสัปดาห์ ครั้งที่</t>
   </si>
 </sst>
 </file>
@@ -388,7 +391,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -456,6 +459,74 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="40" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -468,15 +539,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="4" fontId="5" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -495,65 +557,12 @@
     <xf numFmtId="4" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="40" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="23" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1065,32 +1074,32 @@
       <c r="J5" s="19"/>
     </row>
     <row r="6" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A6" s="49" t="s">
+      <c r="A6" s="50" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="49"/>
-      <c r="C6" s="49"/>
-      <c r="D6" s="49"/>
-      <c r="E6" s="49"/>
-      <c r="F6" s="49"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="49"/>
-      <c r="I6" s="49"/>
-      <c r="J6" s="49"/>
+      <c r="B6" s="50"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="50"/>
+      <c r="F6" s="50"/>
+      <c r="G6" s="50"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
+      <c r="J6" s="50"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="50" t="s">
+      <c r="A7" s="51" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="50"/>
-      <c r="F7" s="50"/>
-      <c r="G7" s="50"/>
-      <c r="H7" s="50"/>
-      <c r="I7" s="50"/>
-      <c r="J7" s="50"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="51"/>
+      <c r="D7" s="51"/>
+      <c r="E7" s="51"/>
+      <c r="F7" s="51"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="51"/>
+      <c r="I7" s="51"/>
+      <c r="J7" s="51"/>
     </row>
     <row r="8" spans="1:10" ht="21.75" x14ac:dyDescent="0.5">
       <c r="A8" s="2"/>
@@ -1114,10 +1123,10 @@
       <c r="G9" s="19"/>
     </row>
     <row r="10" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="51" t="s">
+      <c r="A10" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="51"/>
+      <c r="B10" s="39"/>
       <c r="C10" s="53" t="s">
         <v>31</v>
       </c>
@@ -1141,26 +1150,26 @@
       <c r="E11" s="53"/>
       <c r="F11" s="53"/>
       <c r="G11" s="53"/>
-      <c r="H11" s="54" t="s">
+      <c r="H11" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="I11" s="54"/>
+      <c r="I11" s="38"/>
       <c r="J11" s="16" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A12" s="51" t="s">
+      <c r="A12" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="51"/>
-      <c r="C12" s="55" t="s">
+      <c r="B12" s="39"/>
+      <c r="C12" s="40" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="40"/>
       <c r="H12" s="31"/>
       <c r="I12" s="31"/>
       <c r="J12" s="16"/>
@@ -1178,32 +1187,36 @@
       <c r="J13" s="16"/>
     </row>
     <row r="14" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="56" t="s">
+      <c r="A14" s="41" t="s">
         <v>29</v>
       </c>
-      <c r="B14" s="56"/>
-      <c r="C14" s="57" t="s">
+      <c r="B14" s="41"/>
+      <c r="C14" s="42" t="s">
         <v>30</v>
       </c>
-      <c r="D14" s="57"/>
-      <c r="E14" s="57"/>
-      <c r="F14" s="57"/>
-      <c r="G14" s="57"/>
-      <c r="H14" s="31"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="16"/>
+      <c r="D14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="F14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="67" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="67"/>
+      <c r="J14" s="68">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:10" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="56"/>
-      <c r="B15" s="56"/>
-      <c r="C15" s="57"/>
-      <c r="D15" s="57"/>
-      <c r="E15" s="57"/>
-      <c r="F15" s="57"/>
-      <c r="G15" s="57"/>
-      <c r="H15" s="31"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="16"/>
+      <c r="A15" s="41"/>
+      <c r="B15" s="41"/>
+      <c r="C15" s="42"/>
+      <c r="D15" s="42"/>
+      <c r="E15" s="42"/>
+      <c r="F15" s="42"/>
+      <c r="G15" s="42"/>
+      <c r="H15" s="67"/>
+      <c r="I15" s="67"/>
+      <c r="J15" s="68"/>
     </row>
     <row r="16" spans="1:10" ht="17.25" x14ac:dyDescent="0.3">
       <c r="A16" s="30"/>
@@ -1218,34 +1231,34 @@
       <c r="J16" s="16"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="58" t="s">
+      <c r="A17" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38" t="s">
+      <c r="B17" s="44"/>
+      <c r="C17" s="44" t="s">
         <v>14</v>
       </c>
-      <c r="D17" s="38"/>
-      <c r="E17" s="38"/>
-      <c r="F17" s="38"/>
-      <c r="G17" s="38"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="38" t="s">
+      <c r="D17" s="44"/>
+      <c r="E17" s="44"/>
+      <c r="F17" s="44"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="44"/>
+      <c r="I17" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="J17" s="60"/>
+      <c r="J17" s="47"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="59"/>
-      <c r="B18" s="39"/>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
-      <c r="F18" s="39"/>
-      <c r="G18" s="39"/>
-      <c r="H18" s="39"/>
-      <c r="I18" s="39"/>
-      <c r="J18" s="61"/>
+      <c r="A18" s="45"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="46"/>
+      <c r="E18" s="46"/>
+      <c r="F18" s="46"/>
+      <c r="G18" s="46"/>
+      <c r="H18" s="46"/>
+      <c r="I18" s="46"/>
+      <c r="J18" s="48"/>
     </row>
     <row r="19" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
@@ -1320,19 +1333,19 @@
       <c r="J22" s="6"/>
     </row>
     <row r="23" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
-      <c r="A23" s="62">
+      <c r="A23" s="49">
         <v>5</v>
       </c>
-      <c r="B23" s="62"/>
-      <c r="C23" s="63"/>
-      <c r="D23" s="63"/>
-      <c r="E23" s="63" t="s">
+      <c r="B23" s="49"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="33"/>
+      <c r="E23" s="33" t="s">
         <v>33</v>
       </c>
-      <c r="F23" s="63"/>
-      <c r="G23" s="64"/>
-      <c r="H23" s="65"/>
-      <c r="I23" s="66">
+      <c r="F23" s="33"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="36">
         <v>-12000</v>
       </c>
       <c r="J23" s="6"/>
@@ -1412,57 +1425,57 @@
     <row r="30" spans="1:10" ht="16.5" x14ac:dyDescent="0.3">
       <c r="A30" s="37"/>
       <c r="B30" s="37"/>
-      <c r="C30" s="44"/>
-      <c r="D30" s="44"/>
-      <c r="E30" s="44"/>
-      <c r="F30" s="44"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="44"/>
-      <c r="I30" s="45"/>
-      <c r="J30" s="45"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="65"/>
+      <c r="E30" s="65"/>
+      <c r="F30" s="65"/>
+      <c r="G30" s="65"/>
+      <c r="H30" s="65"/>
+      <c r="I30" s="66"/>
+      <c r="J30" s="66"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" s="46"/>
-      <c r="B31" s="46"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="47"/>
-      <c r="H31" s="47"/>
-      <c r="I31" s="48"/>
-      <c r="J31" s="48"/>
+      <c r="A31" s="54"/>
+      <c r="B31" s="54"/>
+      <c r="C31" s="55"/>
+      <c r="D31" s="55"/>
+      <c r="E31" s="55"/>
+      <c r="F31" s="55"/>
+      <c r="G31" s="55"/>
+      <c r="H31" s="55"/>
+      <c r="I31" s="56"/>
+      <c r="J31" s="56"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="4"/>
       <c r="B32" s="4"/>
-      <c r="C32" s="38" t="s">
+      <c r="C32" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="D32" s="38"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="38"/>
-      <c r="G32" s="38"/>
-      <c r="H32" s="38"/>
-      <c r="I32" s="40">
+      <c r="D32" s="44"/>
+      <c r="E32" s="44"/>
+      <c r="F32" s="44"/>
+      <c r="G32" s="44"/>
+      <c r="H32" s="44"/>
+      <c r="I32" s="61">
         <f>SUM(I19:I31)</f>
         <v>388000</v>
       </c>
-      <c r="J32" s="42" t="s">
+      <c r="J32" s="63" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39"/>
-      <c r="F33" s="39"/>
-      <c r="G33" s="39"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="41"/>
-      <c r="J33" s="43"/>
+      <c r="C33" s="46"/>
+      <c r="D33" s="46"/>
+      <c r="E33" s="46"/>
+      <c r="F33" s="46"/>
+      <c r="G33" s="46"/>
+      <c r="H33" s="46"/>
+      <c r="I33" s="62"/>
+      <c r="J33" s="64"/>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
@@ -1477,64 +1490,64 @@
       <c r="J34" s="2"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" s="33" t="s">
+      <c r="A35" s="57" t="s">
         <v>6</v>
       </c>
-      <c r="B35" s="33"/>
-      <c r="C35" s="33"/>
-      <c r="D35" s="34" t="s">
+      <c r="B35" s="57"/>
+      <c r="C35" s="57"/>
+      <c r="D35" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="35" t="s">
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I35" s="35"/>
-      <c r="J35" s="35"/>
+      <c r="I35" s="59"/>
+      <c r="J35" s="59"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" s="33"/>
-      <c r="B36" s="33"/>
-      <c r="C36" s="33"/>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="35"/>
-      <c r="I36" s="35"/>
-      <c r="J36" s="35"/>
+      <c r="A36" s="57"/>
+      <c r="B36" s="57"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="58"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="58"/>
+      <c r="G36" s="58"/>
+      <c r="H36" s="59"/>
+      <c r="I36" s="59"/>
+      <c r="J36" s="59"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" s="33" t="s">
+      <c r="A37" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="B37" s="33"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="34" t="s">
+      <c r="B37" s="57"/>
+      <c r="C37" s="57"/>
+      <c r="D37" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="34"/>
-      <c r="H37" s="35" t="s">
+      <c r="E37" s="58"/>
+      <c r="F37" s="58"/>
+      <c r="G37" s="58"/>
+      <c r="H37" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="I37" s="35"/>
-      <c r="J37" s="35"/>
+      <c r="I37" s="59"/>
+      <c r="J37" s="59"/>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A38" s="33"/>
-      <c r="B38" s="33"/>
-      <c r="C38" s="33"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="34"/>
-      <c r="F38" s="34"/>
-      <c r="G38" s="34"/>
-      <c r="H38" s="35"/>
-      <c r="I38" s="35"/>
-      <c r="J38" s="35"/>
+      <c r="A38" s="57"/>
+      <c r="B38" s="57"/>
+      <c r="C38" s="57"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="58"/>
+      <c r="H38" s="59"/>
+      <c r="I38" s="59"/>
+      <c r="J38" s="59"/>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="1"/>
@@ -1544,36 +1557,14 @@
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1"/>
-      <c r="H39" s="36" t="s">
+      <c r="H39" s="60" t="s">
         <v>0</v>
       </c>
-      <c r="I39" s="36"/>
-      <c r="J39" s="36"/>
+      <c r="I39" s="60"/>
+      <c r="J39" s="60"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="A26:B26"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="A14:B15"/>
-    <mergeCell ref="C14:G15"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A17:B18"/>
-    <mergeCell ref="C17:H18"/>
-    <mergeCell ref="I17:J18"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="C10:G11"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:H31"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A28:B28"/>
+  <mergeCells count="40">
     <mergeCell ref="A37:C38"/>
     <mergeCell ref="D37:G38"/>
     <mergeCell ref="H37:J38"/>
@@ -1590,6 +1581,30 @@
     <mergeCell ref="A30:B30"/>
     <mergeCell ref="C30:H30"/>
     <mergeCell ref="I30:J30"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="C31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="C10:G11"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="A14:B15"/>
+    <mergeCell ref="C14:G15"/>
+    <mergeCell ref="A20:B20"/>
+    <mergeCell ref="A17:B18"/>
+    <mergeCell ref="C17:H18"/>
+    <mergeCell ref="I17:J18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="H14:I15"/>
+    <mergeCell ref="J14:J15"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
